--- a/SGC-CKN/Excel/e6ac099a-5f17-4c17-83a5-3faf911b17a1_Lô_CT-02_P8_4_D800_04-04-2026.xlsx
+++ b/SGC-CKN/Excel/e6ac099a-5f17-4c17-83a5-3faf911b17a1_Lô_CT-02_P8_4_D800_04-04-2026.xlsx
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>17:40 04/04/2026</t>
+    <t>17:40 03/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">17:40
-04/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">18:08
-04/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t/>
@@ -116,11 +116,11 @@
   </si>
   <si>
     <t xml:space="preserve">18:09
-04/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">18:17
-04/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -130,11 +130,11 @@
   </si>
   <si>
     <t xml:space="preserve">18:18
-04/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">19:30
-04/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>Thay răng gàu từ 18:18 đến 19:15</t>
@@ -147,7 +147,7 @@
   </si>
   <si>
     <t xml:space="preserve">20:00
-04/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -157,7 +157,7 @@
   </si>
   <si>
     <t xml:space="preserve">20:35
-04/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -167,7 +167,7 @@
   </si>
   <si>
     <t xml:space="preserve">21:30
-04/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -177,7 +177,7 @@
   </si>
   <si>
     <t xml:space="preserve">21:55
-04/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -187,7 +187,7 @@
   </si>
   <si>
     <t xml:space="preserve">23:00
-04/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>Có xen sỏi</t>
@@ -1217,7 +1217,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.44</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.99</v>
@@ -1226,10 +1226,10 @@
         <v>0.47</v>
       </c>
       <c r="I11" s="5">
-        <v>3.55</v>
+        <v>6.99</v>
       </c>
       <c r="J11" s="8">
-        <v>7.61</v>
+        <v>14.98</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1360,16 +1360,16 @@
         <v>-21.45</v>
       </c>
       <c r="G15" s="18">
-        <v>-26.98</v>
+        <v>-26.48</v>
       </c>
       <c r="H15" s="18">
         <v>0.58</v>
       </c>
       <c r="I15" s="18">
-        <v>5.53</v>
+        <v>5.03</v>
       </c>
       <c r="J15" s="8">
-        <v>9.48</v>
+        <v>8.62</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
@@ -1392,7 +1392,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="21">
-        <v>-26.98</v>
+        <v>-26.48</v>
       </c>
       <c r="G16" s="21">
         <v>-36</v>
@@ -1401,10 +1401,10 @@
         <v>0.92</v>
       </c>
       <c r="I16" s="21">
-        <v>9.02</v>
+        <v>9.52</v>
       </c>
       <c r="J16" s="8">
-        <v>9.84</v>
+        <v>10.39</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>30</v>
@@ -1699,7 +1699,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.44</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.99</v>
@@ -1708,10 +1708,10 @@
         <v>0.47</v>
       </c>
       <c r="H2" s="5">
-        <v>3.55</v>
+        <v>6.99</v>
       </c>
       <c r="I2" s="8">
-        <v>7.61</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1818,16 +1818,16 @@
         <v>-21.45</v>
       </c>
       <c r="F6" s="18">
-        <v>-26.98</v>
+        <v>-26.48</v>
       </c>
       <c r="G6" s="18">
         <v>0.58</v>
       </c>
       <c r="H6" s="18">
-        <v>5.53</v>
+        <v>5.03</v>
       </c>
       <c r="I6" s="8">
-        <v>9.48</v>
+        <v>8.62</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1844,7 +1844,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="21">
-        <v>-26.98</v>
+        <v>-26.48</v>
       </c>
       <c r="F7" s="21">
         <v>-36</v>
@@ -1853,10 +1853,10 @@
         <v>0.92</v>
       </c>
       <c r="H7" s="21">
-        <v>9.02</v>
+        <v>9.52</v>
       </c>
       <c r="I7" s="8">
-        <v>9.84</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1989,7 +1989,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-3.44</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
         <v>-44.81</v>
@@ -1998,10 +1998,10 @@
         <v>7.72</v>
       </c>
       <c r="H12" s="39">
-        <v>41.37</v>
+        <v>44.81</v>
       </c>
       <c r="I12" s="39">
-        <v>5.36</v>
+        <v>5.81</v>
       </c>
     </row>
   </sheetData>
